--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2582"/>
+  <dimension ref="A1:E2583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70130,6 +70130,33 @@
         </is>
       </c>
     </row>
+    <row r="2583">
+      <c r="A2583" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B2583" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2583" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D2583" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E2583" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2583"/>
+  <dimension ref="A1:E2584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70157,6 +70157,33 @@
         </is>
       </c>
     </row>
+    <row r="2584">
+      <c r="A2584" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2584" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2584" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D2584" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E2584" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2584"/>
+  <dimension ref="A1:E2585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70184,6 +70184,33 @@
         </is>
       </c>
     </row>
+    <row r="2585">
+      <c r="A2585" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2585" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2585" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D2585" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E2585" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="history" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="history" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,31 +425,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2585"/>
+  <dimension ref="A1:E2586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>sorteo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>primero</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>segundo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>tercero</t>
         </is>
@@ -70208,6 +70220,33 @@
       <c r="E2585" t="inlineStr">
         <is>
           <t>78</t>
+        </is>
+      </c>
+    </row>
+    <row r="2586">
+      <c r="A2586" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2586" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2586" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D2586" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E2586" t="inlineStr">
+        <is>
+          <t>57</t>
         </is>
       </c>
     </row>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2586"/>
+  <dimension ref="A1:E2587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70250,6 +70250,33 @@
         </is>
       </c>
     </row>
+    <row r="2587">
+      <c r="A2587" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2587" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2587" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D2587" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E2587" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2587"/>
+  <dimension ref="A1:E2588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70277,6 +70277,33 @@
         </is>
       </c>
     </row>
+    <row r="2588">
+      <c r="A2588" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2588" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2588" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D2588" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E2588" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2588"/>
+  <dimension ref="A1:E2589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70304,6 +70304,33 @@
         </is>
       </c>
     </row>
+    <row r="2589">
+      <c r="A2589" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B2589" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2589" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D2589" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E2589" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2589"/>
+  <dimension ref="A1:E2590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70331,6 +70331,33 @@
         </is>
       </c>
     </row>
+    <row r="2590">
+      <c r="A2590" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B2590" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2590" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="D2590" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E2590" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2590"/>
+  <dimension ref="A1:E2591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70358,6 +70358,33 @@
         </is>
       </c>
     </row>
+    <row r="2591">
+      <c r="A2591" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2591" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2591" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D2591" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E2591" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2591"/>
+  <dimension ref="A1:E2592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70385,6 +70385,33 @@
         </is>
       </c>
     </row>
+    <row r="2592">
+      <c r="A2592" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B2592" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2592" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D2592" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E2592" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2592"/>
+  <dimension ref="A1:E2593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70412,6 +70412,33 @@
         </is>
       </c>
     </row>
+    <row r="2593">
+      <c r="A2593" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B2593" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2593" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D2593" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E2593" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2593"/>
+  <dimension ref="A1:E2594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70439,6 +70439,33 @@
         </is>
       </c>
     </row>
+    <row r="2594">
+      <c r="A2594" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B2594" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2594" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D2594" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E2594" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2594"/>
+  <dimension ref="A1:E2595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70466,6 +70466,33 @@
         </is>
       </c>
     </row>
+    <row r="2595">
+      <c r="A2595" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B2595" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2595" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D2595" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E2595" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2595"/>
+  <dimension ref="A1:E2596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70493,6 +70493,33 @@
         </is>
       </c>
     </row>
+    <row r="2596">
+      <c r="A2596" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B2596" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2596" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D2596" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E2596" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2596"/>
+  <dimension ref="A1:E2597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70520,6 +70520,33 @@
         </is>
       </c>
     </row>
+    <row r="2597">
+      <c r="A2597" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B2597" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2597" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D2597" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="E2597" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2597"/>
+  <dimension ref="A1:E2598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70547,6 +70547,33 @@
         </is>
       </c>
     </row>
+    <row r="2598">
+      <c r="A2598" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B2598" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2598" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D2598" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E2598" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2598"/>
+  <dimension ref="A1:E2599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70574,6 +70574,33 @@
         </is>
       </c>
     </row>
+    <row r="2599">
+      <c r="A2599" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B2599" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2599" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D2599" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E2599" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2599"/>
+  <dimension ref="A1:E2600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70601,6 +70601,33 @@
         </is>
       </c>
     </row>
+    <row r="2600">
+      <c r="A2600" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2600" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2600" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D2600" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E2600" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2600"/>
+  <dimension ref="A1:E2601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70628,6 +70628,33 @@
         </is>
       </c>
     </row>
+    <row r="2601">
+      <c r="A2601" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2601" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2601" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D2601" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E2601" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2601"/>
+  <dimension ref="A1:E2602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70655,6 +70655,33 @@
         </is>
       </c>
     </row>
+    <row r="2602">
+      <c r="A2602" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B2602" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2602" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D2602" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E2602" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2602"/>
+  <dimension ref="A1:E2603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70682,6 +70682,33 @@
         </is>
       </c>
     </row>
+    <row r="2603">
+      <c r="A2603" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B2603" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2603" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D2603" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="E2603" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2603"/>
+  <dimension ref="A1:E2604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70709,6 +70709,33 @@
         </is>
       </c>
     </row>
+    <row r="2604">
+      <c r="A2604" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B2604" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2604" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D2604" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E2604" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2604"/>
+  <dimension ref="A1:E2605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70736,6 +70736,33 @@
         </is>
       </c>
     </row>
+    <row r="2605">
+      <c r="A2605" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B2605" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2605" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D2605" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E2605" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2605"/>
+  <dimension ref="A1:E2606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70763,6 +70763,33 @@
         </is>
       </c>
     </row>
+    <row r="2606">
+      <c r="A2606" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B2606" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2606" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D2606" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="E2606" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2606"/>
+  <dimension ref="A1:E2607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70790,6 +70790,33 @@
         </is>
       </c>
     </row>
+    <row r="2607">
+      <c r="A2607" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2607" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2607" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D2607" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E2607" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2607"/>
+  <dimension ref="A1:E2608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70817,6 +70817,33 @@
         </is>
       </c>
     </row>
+    <row r="2608">
+      <c r="A2608" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B2608" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2608" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D2608" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E2608" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2608"/>
+  <dimension ref="A1:E2609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70844,6 +70844,33 @@
         </is>
       </c>
     </row>
+    <row r="2609">
+      <c r="A2609" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B2609" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2609" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D2609" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E2609" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2609"/>
+  <dimension ref="A1:E2610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70871,6 +70871,33 @@
         </is>
       </c>
     </row>
+    <row r="2610">
+      <c r="A2610" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B2610" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2610" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D2610" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E2610" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2610"/>
+  <dimension ref="A1:E2611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70898,6 +70898,33 @@
         </is>
       </c>
     </row>
+    <row r="2611">
+      <c r="A2611" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B2611" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2611" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D2611" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E2611" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2611"/>
+  <dimension ref="A1:E2612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70925,6 +70925,33 @@
         </is>
       </c>
     </row>
+    <row r="2612">
+      <c r="A2612" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2612" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2612" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D2612" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E2612" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2612"/>
+  <dimension ref="A1:E2613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70952,6 +70952,33 @@
         </is>
       </c>
     </row>
+    <row r="2613">
+      <c r="A2613" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2613" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2613" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D2613" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E2613" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2613"/>
+  <dimension ref="A1:E2614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70979,6 +70979,33 @@
         </is>
       </c>
     </row>
+    <row r="2614">
+      <c r="A2614" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2614" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2614" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D2614" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E2614" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2614"/>
+  <dimension ref="A1:E2615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71006,6 +71006,33 @@
         </is>
       </c>
     </row>
+    <row r="2615">
+      <c r="A2615" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2615" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2615" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D2615" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E2615" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2615"/>
+  <dimension ref="A1:E2616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71033,6 +71033,33 @@
         </is>
       </c>
     </row>
+    <row r="2616">
+      <c r="A2616" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2616" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2616" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D2616" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E2616" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2616"/>
+  <dimension ref="A1:E2617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71060,6 +71060,33 @@
         </is>
       </c>
     </row>
+    <row r="2617">
+      <c r="A2617" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B2617" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2617" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D2617" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E2617" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2617"/>
+  <dimension ref="A1:E2618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71087,6 +71087,33 @@
         </is>
       </c>
     </row>
+    <row r="2618">
+      <c r="A2618" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B2618" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2618" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D2618" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E2618" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2618"/>
+  <dimension ref="A1:E2619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71114,6 +71114,33 @@
         </is>
       </c>
     </row>
+    <row r="2619">
+      <c r="A2619" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2619" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2619" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D2619" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E2619" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2619"/>
+  <dimension ref="A1:E2620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71141,6 +71141,33 @@
         </is>
       </c>
     </row>
+    <row r="2620">
+      <c r="A2620" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2620" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2620" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D2620" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E2620" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2620"/>
+  <dimension ref="A1:E2621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71168,6 +71168,33 @@
         </is>
       </c>
     </row>
+    <row r="2621">
+      <c r="A2621" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2621" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2621" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D2621" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E2621" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2621"/>
+  <dimension ref="A1:E2622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71195,6 +71195,33 @@
         </is>
       </c>
     </row>
+    <row r="2622">
+      <c r="A2622" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2622" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2622" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D2622" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E2622" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2622"/>
+  <dimension ref="A1:E2623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71222,6 +71222,33 @@
         </is>
       </c>
     </row>
+    <row r="2623">
+      <c r="A2623" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2623" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2623" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D2623" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E2623" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2623"/>
+  <dimension ref="A1:E2624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71249,6 +71249,33 @@
         </is>
       </c>
     </row>
+    <row r="2624">
+      <c r="A2624" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B2624" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2624" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D2624" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E2624" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2624"/>
+  <dimension ref="A1:E2625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71276,6 +71276,33 @@
         </is>
       </c>
     </row>
+    <row r="2625">
+      <c r="A2625" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B2625" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2625" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D2625" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E2625" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2625"/>
+  <dimension ref="A1:E2626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71303,6 +71303,33 @@
         </is>
       </c>
     </row>
+    <row r="2626">
+      <c r="A2626" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2626" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2626" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D2626" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E2626" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2626"/>
+  <dimension ref="A1:E2627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71330,6 +71330,33 @@
         </is>
       </c>
     </row>
+    <row r="2627">
+      <c r="A2627" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2627" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2627" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D2627" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E2627" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2627"/>
+  <dimension ref="A1:E2628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71357,6 +71357,33 @@
         </is>
       </c>
     </row>
+    <row r="2628">
+      <c r="A2628" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2628" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2628" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D2628" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E2628" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2628"/>
+  <dimension ref="A1:E2629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71384,6 +71384,33 @@
         </is>
       </c>
     </row>
+    <row r="2629">
+      <c r="A2629" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2629" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2629" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D2629" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E2629" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2629"/>
+  <dimension ref="A1:E2630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71411,6 +71411,33 @@
         </is>
       </c>
     </row>
+    <row r="2630">
+      <c r="A2630" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2630" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2630" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D2630" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E2630" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
